--- a/data/trans_orig/P57B5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido rebosante de energía en 2023</t>
+          <t>Población según se ha sentido rebosante de energía en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>226911</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282555</t>
+          <t>283387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>175803</t>
+          <t>177285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217485</t>
+          <t>217378</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>417649</t>
+          <t>414602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>489650</t>
+          <t>490288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>187362</t>
+          <t>186284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236333</t>
+          <t>236244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>247254</t>
+          <t>249167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>288089</t>
+          <t>287313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>446104</t>
+          <t>447342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>511643</t>
+          <t>515162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112936</t>
+          <t>112409</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152137</t>
+          <t>152848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135256</t>
+          <t>135057</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>167836</t>
+          <t>164704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>258311</t>
+          <t>256512</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>309048</t>
+          <t>308090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25680</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>46932</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47609</t>
+          <t>48209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>69199</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77268</t>
+          <t>78451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108589</t>
+          <t>107250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>493891</t>
+          <t>494330</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>896631</t>
+          <t>930688</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>285439</t>
+          <t>286576</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>337673</t>
+          <t>337726</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>793265</t>
+          <t>793471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1338598</t>
+          <t>1433747</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>202383</t>
+          <t>176259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>490344</t>
+          <t>489629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>374444</t>
+          <t>373480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>425365</t>
+          <t>424816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>534117</t>
+          <t>474886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>891719</t>
+          <t>890549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66633</t>
+          <t>66919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169585</t>
+          <t>171113</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>167920</t>
+          <t>169159</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207573</t>
+          <t>208097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>213248</t>
+          <t>196128</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365688</t>
+          <t>363821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>19818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55601</t>
+          <t>57304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46719</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70678</t>
+          <t>70248</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64011</t>
+          <t>61385</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>117296</t>
+          <t>115419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>268199</t>
+          <t>272800</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334300</t>
+          <t>335897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>126690</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315129</t>
+          <t>315235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>356515</t>
+          <t>343583</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>637989</t>
+          <t>633369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>249104</t>
+          <t>249121</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311452</t>
+          <t>311001</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>410771</t>
+          <t>410804</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>725222</t>
+          <t>724415</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>679377</t>
+          <t>681189</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1089040</t>
+          <t>1116125</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84796</t>
+          <t>84711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126367</t>
+          <t>123060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60147</t>
+          <t>62440</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158797</t>
+          <t>163248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152451</t>
+          <t>139491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>266212</t>
+          <t>265919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31797</t>
+          <t>30904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17394</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52872</t>
+          <t>53069</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37565</t>
+          <t>37692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74217</t>
+          <t>74988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>314049</t>
+          <t>309130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>378760</t>
+          <t>376675</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>239257</t>
+          <t>240510</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>325357</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>564754</t>
+          <t>561253</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>689618</t>
+          <t>683812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358134</t>
+          <t>362547</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>425989</t>
+          <t>427539</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>440473</t>
+          <t>438525</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>600285</t>
+          <t>603742</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>824992</t>
+          <t>822886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1017520</t>
+          <t>1015947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>127772</t>
+          <t>126828</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>173306</t>
+          <t>170299</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>188145</t>
+          <t>185669</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>262037</t>
+          <t>262820</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>339230</t>
+          <t>335503</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>419277</t>
+          <t>416137</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>29542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53385</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55654</t>
+          <t>57596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93793</t>
+          <t>93991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93070</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>137134</t>
+          <t>139113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1384710</t>
+          <t>1386095</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2007510</t>
+          <t>2037101</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>842755</t>
+          <t>840669</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1123970</t>
+          <t>1128748</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2586330</t>
+          <t>2586331</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2348496</t>
+          <t>2339581</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3114033</t>
+          <t>3132339</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>963695</t>
+          <t>946436</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1375661</t>
+          <t>1380549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1547874</t>
+          <t>1542845</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2105454</t>
+          <t>2069430</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2682597</t>
+          <t>2662257</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3351969</t>
+          <t>3330640</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,89%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>387416</t>
+          <t>383747</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>571091</t>
+          <t>564978</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>551040</t>
+          <t>567094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>749648</t>
+          <t>756029</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1042357</t>
+          <t>1044341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1300598</t>
+          <t>1297988</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>103210</t>
+          <t>101090</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>161817</t>
+          <t>157080</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>181624</t>
+          <t>185491</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>256074</t>
+          <t>259761</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>312689</t>
+          <t>310195</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>403442</t>
+          <t>400583</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7102823</t>
+          <t>7102824</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">

--- a/data/trans_orig/P57B5_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B5_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>253886</t>
+          <t>274757</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>225857</t>
+          <t>245972</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>283387</t>
+          <t>303442</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>197334</t>
+          <t>217108</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177285</t>
+          <t>193266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>217378</t>
+          <t>238197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>451220</t>
+          <t>491866</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>414602</t>
+          <t>456539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>490288</t>
+          <t>532944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>211024</t>
+          <t>232866</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186284</t>
+          <t>206365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236244</t>
+          <t>260113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>267197</t>
+          <t>291949</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249167</t>
+          <t>270635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287313</t>
+          <t>313146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>478221</t>
+          <t>524815</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>447342</t>
+          <t>491710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515162</t>
+          <t>560858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132714</t>
+          <t>142631</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112409</t>
+          <t>122154</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152848</t>
+          <t>164361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149945</t>
+          <t>159578</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135057</t>
+          <t>142627</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>164704</t>
+          <t>177581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>282659</t>
+          <t>302210</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256512</t>
+          <t>277220</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>308090</t>
+          <t>329686</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34900</t>
+          <t>37370</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>27589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46932</t>
+          <t>51542</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>61032</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48209</t>
+          <t>51489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69199</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92788</t>
+          <t>98402</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78451</t>
+          <t>83982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107250</t>
+          <t>116606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>632524</t>
+          <t>687624</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>632524</t>
+          <t>687624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>632524</t>
+          <t>687624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>672364</t>
+          <t>729667</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>672364</t>
+          <t>729667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>672364</t>
+          <t>729667</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1304888</t>
+          <t>1417292</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1304888</t>
+          <t>1417292</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1304888</t>
+          <t>1417292</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>649784</t>
+          <t>446072</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>494330</t>
+          <t>411389</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>930688</t>
+          <t>484334</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>310894</t>
+          <t>344553</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>286576</t>
+          <t>313994</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>337726</t>
+          <t>374825</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>960679</t>
+          <t>790625</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>793471</t>
+          <t>743642</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1433747</t>
+          <t>844531</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>377345</t>
+          <t>422404</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>176259</t>
+          <t>385300</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>489629</t>
+          <t>457829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>399913</t>
+          <t>453957</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>373480</t>
+          <t>424101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>424816</t>
+          <t>487432</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>777258</t>
+          <t>876361</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>474886</t>
+          <t>829469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>890549</t>
+          <t>919058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>43,45%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>127261</t>
+          <t>139798</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66919</t>
+          <t>119753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171113</t>
+          <t>164447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>186457</t>
+          <t>205959</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169159</t>
+          <t>185569</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>208097</t>
+          <t>229029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>313719</t>
+          <t>345756</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196128</t>
+          <t>316121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363821</t>
+          <t>375480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,75%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>37664</t>
+          <t>39755</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19818</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57304</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57277</t>
+          <t>62546</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>51831</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70248</t>
+          <t>77012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>94941</t>
+          <t>102301</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61385</t>
+          <t>85389</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115419</t>
+          <t>122596</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192054</t>
+          <t>1048029</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192054</t>
+          <t>1048029</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192054</t>
+          <t>1048029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>954541</t>
+          <t>1067015</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>954541</t>
+          <t>1067015</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>954541</t>
+          <t>1067015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2146596</t>
+          <t>2115044</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2146596</t>
+          <t>2115044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2146596</t>
+          <t>2115044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>303128</t>
+          <t>345368</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>272800</t>
+          <t>313203</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335897</t>
+          <t>374580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>234743</t>
+          <t>271908</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>126690</t>
+          <t>245499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315235</t>
+          <t>299012</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>537871</t>
+          <t>617276</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343583</t>
+          <t>579372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>633369</t>
+          <t>660974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>278286</t>
+          <t>318534</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>249121</t>
+          <t>289054</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311001</t>
+          <t>350799</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>539949</t>
+          <t>352112</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>410804</t>
+          <t>325921</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>724415</t>
+          <t>378978</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>818235</t>
+          <t>670646</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>681189</t>
+          <t>626223</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1116125</t>
+          <t>710079</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>44,04%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>102483</t>
+          <t>115922</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84711</t>
+          <t>96003</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123060</t>
+          <t>138210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>119254</t>
+          <t>143645</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62440</t>
+          <t>125070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163248</t>
+          <t>166445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>221738</t>
+          <t>259567</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139491</t>
+          <t>231412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>265919</t>
+          <t>289209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>22538</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30904</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37386</t>
+          <t>42388</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>32706</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>54362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>64925</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37692</t>
+          <t>51466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74988</t>
+          <t>82846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704071</t>
+          <t>802362</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704071</t>
+          <t>802362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704071</t>
+          <t>802362</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>931333</t>
+          <t>810052</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931333</t>
+          <t>810052</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931333</t>
+          <t>810052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1635404</t>
+          <t>1612414</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1635404</t>
+          <t>1612414</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1635404</t>
+          <t>1612414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>343790</t>
+          <t>373364</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>309130</t>
+          <t>340180</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>376675</t>
+          <t>407741</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>292771</t>
+          <t>326844</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>240510</t>
+          <t>299553</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>355061</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>636561</t>
+          <t>700208</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>561253</t>
+          <t>657063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>683812</t>
+          <t>745260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,4%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>393060</t>
+          <t>417233</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>362547</t>
+          <t>383632</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>427539</t>
+          <t>450471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>491608</t>
+          <t>460562</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>438525</t>
+          <t>428341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>603742</t>
+          <t>487968</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>884668</t>
+          <t>877794</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>822886</t>
+          <t>835191</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1015947</t>
+          <t>921865</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>147641</t>
+          <t>153058</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>126828</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>170299</t>
+          <t>177931</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>233724</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>185669</t>
+          <t>230311</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>262820</t>
+          <t>280071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>381365</t>
+          <t>407815</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335503</t>
+          <t>376717</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>416137</t>
+          <t>441759</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>39920</t>
+          <t>43890</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52442</t>
+          <t>59062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>73421</t>
+          <t>75632</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57596</t>
+          <t>62127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>93991</t>
+          <t>90418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>113341</t>
+          <t>119522</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94264</t>
+          <t>100945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139113</t>
+          <t>140443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>924411</t>
+          <t>987545</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>924411</t>
+          <t>987545</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>924411</t>
+          <t>987545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1091524</t>
+          <t>1117795</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1091524</t>
+          <t>1117795</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1091524</t>
+          <t>1117795</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2015936</t>
+          <t>2105339</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2015936</t>
+          <t>2105339</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2015936</t>
+          <t>2105339</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1550589</t>
+          <t>1439562</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1386095</t>
+          <t>1368687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2037101</t>
+          <t>1506083</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1035742</t>
+          <t>1160413</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>840669</t>
+          <t>1103036</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1128748</t>
+          <t>1211450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2586331</t>
+          <t>2599975</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2339581</t>
+          <t>2511928</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3132339</t>
+          <t>2687293</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1259715</t>
+          <t>1391037</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>946436</t>
+          <t>1326609</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1380549</t>
+          <t>1456064</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1698668</t>
+          <t>1558579</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1542845</t>
+          <t>1503497</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2069430</t>
+          <t>1613350</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2958382</t>
+          <t>2949616</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2662257</t>
+          <t>2865490</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3330640</t>
+          <t>3033907</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>510100</t>
+          <t>551409</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>383747</t>
+          <t>508398</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>564978</t>
+          <t>597123</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>689381</t>
+          <t>763939</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>567094</t>
+          <t>722522</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>756029</t>
+          <t>804719</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1199481</t>
+          <t>1315348</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1044341</t>
+          <t>1253253</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1297988</t>
+          <t>1380159</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>132658</t>
+          <t>143552</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>101090</t>
+          <t>123417</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>157080</t>
+          <t>168869</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>225973</t>
+          <t>241598</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>185491</t>
+          <t>218882</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>259761</t>
+          <t>267511</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>358630</t>
+          <t>385151</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>310195</t>
+          <t>350008</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>400583</t>
+          <t>419181</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3453061</t>
+          <t>3525560</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3649763</t>
+          <t>3724529</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7102824</t>
+          <t>7250090</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
